--- a/doc/SAMPA.xlsx
+++ b/doc/SAMPA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveunibo-my.sharepoint.com/personal/francesca_schiavon10_studio_unibo_it/Documents/Desktop/IMT/TESI/linguistic_pipeline_EEG/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="201" documentId="13_ncr:1_{98287EBF-F856-4535-87FC-EEF080BA305D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80F80F0D-56EC-496E-A453-A761CE7282E8}"/>
+  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{98287EBF-F856-4535-87FC-EEF080BA305D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F2C0A83-779D-495C-AF2F-D8EF97D54D31}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{F3F3F33F-9DC9-4C03-8C42-A9B596956D04}"/>
+    <workbookView xWindow="19090" yWindow="1920" windowWidth="19420" windowHeight="11500" xr2:uid="{F3F3F33F-9DC9-4C03-8C42-A9B596956D04}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="104">
   <si>
     <t>SAMPA</t>
   </si>
@@ -281,9 +284,6 @@
     <t>N</t>
   </si>
   <si>
-    <t>ɳ</t>
-  </si>
-  <si>
     <t>g:</t>
   </si>
   <si>
@@ -339,6 +339,18 @@
   </si>
   <si>
     <t>OO</t>
+  </si>
+  <si>
+    <t>ŋ</t>
+  </si>
+  <si>
+    <t>NN</t>
+  </si>
+  <si>
+    <t>ŋ:</t>
+  </si>
+  <si>
+    <t>SS</t>
   </si>
 </sst>
 </file>
@@ -405,8 +417,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -426,7 +438,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -742,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BB01CAE-CDD2-47B0-BCB0-5F1ED8FD89F4}">
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
@@ -884,7 +896,7 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
@@ -892,288 +904,288 @@
         <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
-      </c>
-      <c r="C50" s="3"/>
+        <v>84</v>
+      </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="C51" s="3"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="B53" t="s">
-        <v>6</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
@@ -1181,79 +1193,87 @@
         <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B58" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B60" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B62" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
